--- a/fmea_recommender/tables/all_iso.xlsx
+++ b/fmea_recommender/tables/all_iso.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christodoulosconstantinides/Desktop/research/autoq/AutoQA/fmea_recommender/iso_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97353D8C-2671-A14C-B356-0BA26A7F2727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C2205D-53F6-E74B-BF84-F9A9B91676C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2200" windowWidth="28040" windowHeight="17440" activeTab="9" xr2:uid="{F87957DB-7841-2E43-AEE4-8489BA40EBCC}"/>
+    <workbookView xWindow="3900" yWindow="2200" windowWidth="28040" windowHeight="17440" activeTab="2" xr2:uid="{F87957DB-7841-2E43-AEE4-8489BA40EBCC}"/>
   </bookViews>
   <sheets>
     <sheet name="drilling_equipment" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="361">
   <si>
     <t>Equipment class code</t>
   </si>
@@ -990,9 +990,6 @@
   </si>
   <si>
     <t>Lubricant, cooling water, hydraulic fluid, methanol, etc</t>
-  </si>
-  <si>
-    <t>HIC)</t>
   </si>
   <si>
     <t>Leakage internally of process fluids</t>
@@ -1522,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -1545,10 +1542,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F2" t="s">
         <v>350</v>
-      </c>
-      <c r="F2" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1839,7 +1836,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>354</v>
       </c>
       <c r="B20" t="s">
         <v>59</v>
@@ -2033,10 +2030,10 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -2050,10 +2047,10 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E2" t="s">
         <v>324</v>
-      </c>
-      <c r="E2" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -2078,7 +2075,7 @@
         <v>94</v>
       </c>
       <c r="B4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C4" t="s">
         <v>295</v>
@@ -2132,7 +2129,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -2268,7 +2265,7 @@
         <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -2276,7 +2273,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>315</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
         <v>42</v>
@@ -2296,7 +2293,7 @@
         <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -2313,7 +2310,7 @@
         <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -2355,7 +2352,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>354</v>
       </c>
       <c r="B21" t="s">
         <v>59</v>
@@ -2375,7 +2372,7 @@
         <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C22" t="s">
         <v>63</v>
@@ -2451,13 +2448,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>331</v>
+      </c>
+      <c r="B27" t="s">
         <v>332</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>333</v>
-      </c>
-      <c r="C27" t="s">
-        <v>334</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -2950,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -3165,7 +3162,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>354</v>
       </c>
       <c r="B17" t="s">
         <v>59</v>
@@ -3327,7 +3324,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B42E58-0982-9D49-8347-0A744364E4F3}">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -3338,60 +3335,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
       <c r="C2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>167</v>
+        <v>351</v>
       </c>
       <c r="E2" t="s">
-        <v>342</v>
+        <v>170</v>
       </c>
       <c r="F2" t="s">
-        <v>168</v>
+        <v>352</v>
       </c>
       <c r="G2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>352</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
-        <v>170</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>353</v>
-      </c>
-      <c r="G3" t="s">
-        <v>171</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>172</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -3399,13 +3407,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="C5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -3413,97 +3421,103 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>175</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
       </c>
       <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
-      </c>
-      <c r="E7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>179</v>
-      </c>
-      <c r="G11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3515,29 +3529,23 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>180</v>
-      </c>
-      <c r="D12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
+        <v>181</v>
+      </c>
+      <c r="G12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>181</v>
-      </c>
-      <c r="G13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3549,21 +3557,21 @@
         <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>182</v>
-      </c>
-      <c r="F14" t="s">
+        <v>183</v>
+      </c>
+      <c r="G14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G15" t="s">
         <v>10</v>
@@ -3571,27 +3579,27 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
-      </c>
-      <c r="G16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F17" t="s">
         <v>10</v>
@@ -3599,13 +3607,16 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
+        <v>187</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>10</v>
@@ -3613,16 +3624,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>187</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
+        <v>188</v>
       </c>
       <c r="F19" t="s">
         <v>10</v>
@@ -3630,29 +3638,35 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>188</v>
-      </c>
-      <c r="F20" t="s">
+        <v>189</v>
+      </c>
+      <c r="G20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>189</v>
-      </c>
-      <c r="G21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3664,27 +3678,30 @@
         <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>190</v>
-      </c>
-      <c r="D22" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
+        <v>191</v>
+      </c>
+      <c r="G22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>191</v>
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
       </c>
       <c r="G23" t="s">
         <v>10</v>
@@ -3692,13 +3709,13 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -3707,63 +3724,54 @@
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C25" t="s">
-        <v>192</v>
-      </c>
-      <c r="D25" t="s">
-        <v>10</v>
+        <v>193</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>193</v>
+        <v>72</v>
+      </c>
+      <c r="D26" t="s">
+        <v>10</v>
       </c>
       <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
+        <v>194</v>
+      </c>
+      <c r="G27" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3775,57 +3783,63 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>194</v>
-      </c>
-      <c r="G28" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
+      </c>
       <c r="C29" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
+        <v>195</v>
+      </c>
+      <c r="E29" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>195</v>
+        <v>84</v>
+      </c>
+      <c r="D30" t="s">
+        <v>10</v>
       </c>
       <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3837,39 +3851,31 @@
         <v>164</v>
       </c>
       <c r="C32" t="s">
-        <v>165</v>
-      </c>
-      <c r="F32" t="s">
+        <v>196</v>
+      </c>
+      <c r="G32" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" t="s">
+        <v>86</v>
+      </c>
       <c r="C33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G33" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" t="s">
-        <v>86</v>
-      </c>
-      <c r="C34" t="s">
-        <v>197</v>
-      </c>
-      <c r="G34" t="s">
-        <v>10</v>
-      </c>
+      <c r="A34" s="2"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3896,7 +3902,7 @@
         <v>199</v>
       </c>
       <c r="F1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G1" t="s">
         <v>200</v>
@@ -3905,7 +3911,7 @@
         <v>201</v>
       </c>
       <c r="I1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J1" t="s">
         <v>202</v>
@@ -3914,7 +3920,7 @@
         <v>203</v>
       </c>
       <c r="L1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -4369,7 +4375,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>354</v>
       </c>
       <c r="B23" t="s">
         <v>59</v>
@@ -4698,85 +4704,117 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F86D2D8-EE2B-9E4B-8CAE-40E076F9905A}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="2"/>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G1" t="s">
+        <v>231</v>
+      </c>
+      <c r="H1" t="s">
+        <v>335</v>
+      </c>
+      <c r="I1" t="s">
+        <v>336</v>
+      </c>
+      <c r="J1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K1" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
       <c r="C2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F2" t="s">
-        <v>335</v>
+        <v>235</v>
       </c>
       <c r="G2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H2" t="s">
-        <v>336</v>
+        <v>237</v>
       </c>
       <c r="I2" t="s">
-        <v>337</v>
+        <v>238</v>
       </c>
       <c r="J2" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="K2" t="s">
-        <v>338</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>233</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>234</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>235</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>236</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>237</v>
+        <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>238</v>
+        <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>239</v>
+        <v>10</v>
       </c>
       <c r="K3" t="s">
-        <v>240</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>241</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -4805,21 +4843,18 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>241</v>
+        <v>176</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
         <v>10</v>
       </c>
       <c r="G5" t="s">
@@ -4840,67 +4875,70 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>242</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>243</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>244</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" t="s">
-        <v>10</v>
-      </c>
       <c r="H6" t="s">
         <v>10</v>
       </c>
-      <c r="I6" t="s">
-        <v>10</v>
-      </c>
       <c r="J6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C7" t="s">
-        <v>244</v>
-      </c>
-      <c r="D7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="H7" t="s">
         <v>10</v>
       </c>
+      <c r="I7" t="s">
+        <v>10</v>
+      </c>
       <c r="J7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C8" t="s">
-        <v>213</v>
+        <v>247</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
       </c>
       <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
         <v>10</v>
       </c>
       <c r="H8" t="s">
@@ -4918,13 +4956,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>246</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -4953,21 +4991,18 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>248</v>
+        <v>186</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
         <v>10</v>
       </c>
       <c r="G10" t="s">
@@ -4988,21 +5023,18 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" t="s">
         <v>10</v>
       </c>
       <c r="H11" t="s">
@@ -5020,18 +5052,24 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
       </c>
       <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
         <v>10</v>
       </c>
       <c r="H12" t="s">
@@ -5049,13 +5087,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -5084,13 +5122,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
@@ -5119,13 +5157,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>134</v>
       </c>
       <c r="C15" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -5154,24 +5192,18 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" t="s">
         <v>10</v>
       </c>
       <c r="H16" t="s">
@@ -5189,18 +5221,24 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>249</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
       <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
         <v>10</v>
       </c>
       <c r="H17" t="s">
@@ -5218,13 +5256,13 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -5253,13 +5291,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -5271,30 +5309,18 @@
         <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" t="s">
-        <v>10</v>
-      </c>
-      <c r="I19" t="s">
-        <v>10</v>
-      </c>
-      <c r="J19" t="s">
-        <v>10</v>
-      </c>
-      <c r="K19" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -5306,18 +5332,30 @@
         <v>10</v>
       </c>
       <c r="G20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -5346,13 +5384,13 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
@@ -5381,13 +5419,13 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>163</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -5415,42 +5453,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>197</v>
-      </c>
-      <c r="D24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" t="s">
-        <v>10</v>
-      </c>
-      <c r="H24" t="s">
-        <v>10</v>
-      </c>
-      <c r="I24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
+      <c r="A24" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5476,7 +5479,7 @@
         <v>252</v>
       </c>
       <c r="F1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G1" t="s">
         <v>253</v>
@@ -5858,7 +5861,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>354</v>
       </c>
       <c r="B21" t="s">
         <v>59</v>
@@ -6184,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E1" t="s">
         <v>283</v>
@@ -6199,7 +6202,7 @@
         <v>286</v>
       </c>
       <c r="I1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J1" t="s">
         <v>287</v>
@@ -6231,7 +6234,7 @@
         <v>292</v>
       </c>
       <c r="I2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J2" t="s">
         <v>293</v>
@@ -6639,7 +6642,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>354</v>
       </c>
       <c r="B23" t="s">
         <v>59</v>
@@ -6883,7 +6886,7 @@
         <v>308</v>
       </c>
       <c r="E1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F1" t="s">
         <v>309</v>
@@ -6959,7 +6962,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -7007,7 +7010,7 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -7038,7 +7041,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -7063,7 +7066,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>315</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
         <v>42</v>
@@ -7083,7 +7086,7 @@
         <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F14" t="s">
         <v>10</v>
@@ -7128,7 +7131,7 @@
         <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -7164,13 +7167,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B20" t="s">
         <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -7190,7 +7193,7 @@
         <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -7218,7 +7221,7 @@
         <v>135</v>
       </c>
       <c r="C23" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -7235,7 +7238,7 @@
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -7252,7 +7255,7 @@
         <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -7311,13 +7314,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>319</v>
+      </c>
+      <c r="B29" t="s">
         <v>320</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>321</v>
-      </c>
-      <c r="C29" t="s">
-        <v>322</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>

--- a/fmea_recommender/tables/all_iso.xlsx
+++ b/fmea_recommender/tables/all_iso.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christodoulosconstantinides/Desktop/research/autoq/AutoQA/fmea_recommender/iso_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/var/folders/1z/rhghrxrd7ds2qf_kf_c6z7yw0000gn/T/fz3temp-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C2205D-53F6-E74B-BF84-F9A9B91676C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C8DF54-C03F-E449-9143-7187410562E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2200" windowWidth="28040" windowHeight="17440" activeTab="2" xr2:uid="{F87957DB-7841-2E43-AEE4-8489BA40EBCC}"/>
+    <workbookView xWindow="3900" yWindow="2200" windowWidth="28040" windowHeight="17440" activeTab="3" xr2:uid="{F87957DB-7841-2E43-AEE4-8489BA40EBCC}"/>
   </bookViews>
   <sheets>
     <sheet name="drilling_equipment" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="360">
   <si>
     <t>Equipment class code</t>
   </si>
@@ -219,9 +219,6 @@
   </si>
   <si>
     <t>Overheating</t>
-  </si>
-  <si>
-    <t>0TH</t>
   </si>
   <si>
     <t>Other</t>
@@ -1519,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -1542,10 +1539,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F2" t="s">
         <v>349</v>
-      </c>
-      <c r="F2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -1836,13 +1833,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s">
         <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -1856,13 +1853,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
         <v>61</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -1873,13 +1870,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
         <v>64</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>65</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -1887,13 +1884,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
         <v>67</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>69</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -1904,13 +1901,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="s">
         <v>70</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>71</v>
-      </c>
-      <c r="C24" t="s">
-        <v>72</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -1924,13 +1921,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
         <v>73</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>74</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -1944,13 +1941,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s">
         <v>76</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>77</v>
-      </c>
-      <c r="C26" t="s">
-        <v>78</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -1964,13 +1961,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s">
         <v>79</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>80</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -1978,13 +1975,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
         <v>82</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>84</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -1998,13 +1995,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
         <v>85</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>86</v>
-      </c>
-      <c r="C29" t="s">
-        <v>87</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -2030,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -2047,21 +2044,21 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E2" t="s">
         <v>323</v>
-      </c>
-      <c r="E2" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
         <v>90</v>
       </c>
-      <c r="B3" t="s">
-        <v>91</v>
-      </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2072,13 +2069,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -2089,13 +2086,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" t="s">
         <v>144</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>145</v>
-      </c>
-      <c r="C5" t="s">
-        <v>146</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -2129,7 +2126,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -2259,13 +2256,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" t="s">
         <v>110</v>
       </c>
-      <c r="B15" t="s">
-        <v>111</v>
-      </c>
       <c r="C15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -2287,13 +2284,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
         <v>116</v>
       </c>
-      <c r="B17" t="s">
-        <v>117</v>
-      </c>
       <c r="C17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -2304,13 +2301,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" t="s">
         <v>118</v>
       </c>
-      <c r="B18" t="s">
-        <v>119</v>
-      </c>
       <c r="C18" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -2352,13 +2349,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
         <v>59</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -2369,13 +2366,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
@@ -2386,13 +2383,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" t="s">
         <v>136</v>
       </c>
-      <c r="B23" t="s">
-        <v>137</v>
-      </c>
       <c r="C23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -2403,13 +2400,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
         <v>138</v>
       </c>
-      <c r="B24" t="s">
-        <v>139</v>
-      </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -2417,13 +2414,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" t="s">
         <v>67</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>68</v>
-      </c>
-      <c r="C25" t="s">
-        <v>69</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -2431,13 +2428,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" t="s">
         <v>73</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>75</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -2448,13 +2445,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>330</v>
+      </c>
+      <c r="B27" t="s">
         <v>331</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>332</v>
-      </c>
-      <c r="C27" t="s">
-        <v>333</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -2465,13 +2462,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
         <v>82</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>84</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -2499,13 +2496,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" t="s">
         <v>88</v>
-      </c>
-      <c r="C1" t="s">
-        <v>89</v>
       </c>
       <c r="F1" s="1"/>
     </row>
@@ -2520,28 +2517,28 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
         <v>90</v>
-      </c>
-      <c r="B3" t="s">
-        <v>91</v>
       </c>
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" t="s">
         <v>92</v>
-      </c>
-      <c r="B4" t="s">
-        <v>93</v>
       </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" t="s">
         <v>94</v>
-      </c>
-      <c r="B5" t="s">
-        <v>95</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -2589,37 +2586,37 @@
     </row>
     <row r="10" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" t="s">
         <v>96</v>
-      </c>
-      <c r="B10" t="s">
-        <v>97</v>
       </c>
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" t="s">
         <v>98</v>
-      </c>
-      <c r="B11" t="s">
-        <v>99</v>
       </c>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" t="s">
         <v>100</v>
-      </c>
-      <c r="B12" t="s">
-        <v>101</v>
       </c>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" t="s">
         <v>102</v>
-      </c>
-      <c r="B13" t="s">
-        <v>103</v>
       </c>
       <c r="F13" s="1"/>
     </row>
@@ -2661,10 +2658,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
         <v>104</v>
-      </c>
-      <c r="B17" t="s">
-        <v>105</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -2673,10 +2670,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" t="s">
         <v>106</v>
-      </c>
-      <c r="B18" t="s">
-        <v>107</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -2697,10 +2694,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" t="s">
         <v>108</v>
-      </c>
-      <c r="B20" t="s">
-        <v>109</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -2721,10 +2718,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" t="s">
         <v>110</v>
-      </c>
-      <c r="B22" t="s">
-        <v>111</v>
       </c>
       <c r="F22" s="1"/>
     </row>
@@ -2739,43 +2736,43 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" t="s">
         <v>112</v>
-      </c>
-      <c r="B24" t="s">
-        <v>113</v>
       </c>
       <c r="F24" s="1"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" t="s">
         <v>114</v>
-      </c>
-      <c r="B25" t="s">
-        <v>115</v>
       </c>
       <c r="F25" s="1"/>
     </row>
     <row r="26" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" t="s">
         <v>116</v>
-      </c>
-      <c r="B26" t="s">
-        <v>117</v>
       </c>
       <c r="F26" s="1"/>
     </row>
     <row r="27" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" t="s">
         <v>118</v>
-      </c>
-      <c r="B27" t="s">
-        <v>119</v>
       </c>
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
@@ -2784,10 +2781,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>120</v>
+      </c>
+      <c r="B29" t="s">
         <v>121</v>
-      </c>
-      <c r="B29" t="s">
-        <v>122</v>
       </c>
       <c r="F29" s="1"/>
     </row>
@@ -2802,19 +2799,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" t="s">
         <v>123</v>
-      </c>
-      <c r="B31" t="s">
-        <v>124</v>
       </c>
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" t="s">
         <v>125</v>
-      </c>
-      <c r="B32" t="s">
-        <v>126</v>
       </c>
       <c r="F32" s="1"/>
     </row>
@@ -2829,10 +2826,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" t="s">
         <v>127</v>
-      </c>
-      <c r="B34" t="s">
-        <v>128</v>
       </c>
       <c r="F34" s="1"/>
     </row>
@@ -2847,10 +2844,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B36" t="s">
         <v>129</v>
-      </c>
-      <c r="B36" t="s">
-        <v>130</v>
       </c>
       <c r="F36" s="1"/>
     </row>
@@ -2865,46 +2862,46 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>353</v>
+      </c>
+      <c r="B38" t="s">
         <v>58</v>
-      </c>
-      <c r="B38" t="s">
-        <v>59</v>
       </c>
       <c r="F38" s="1"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>130</v>
+      </c>
+      <c r="B39" t="s">
         <v>131</v>
-      </c>
-      <c r="B39" t="s">
-        <v>132</v>
       </c>
       <c r="F39" s="1"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>132</v>
+      </c>
+      <c r="B40" t="s">
         <v>133</v>
-      </c>
-      <c r="B40" t="s">
-        <v>134</v>
       </c>
       <c r="F40" s="1"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F41" s="1"/>
     </row>
     <row r="42" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" t="s">
         <v>64</v>
-      </c>
-      <c r="B42" t="s">
-        <v>65</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
@@ -2913,19 +2910,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>135</v>
+      </c>
+      <c r="B43" t="s">
         <v>136</v>
-      </c>
-      <c r="B43" t="s">
-        <v>137</v>
       </c>
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>137</v>
+      </c>
+      <c r="B44" t="s">
         <v>138</v>
-      </c>
-      <c r="B44" t="s">
-        <v>139</v>
       </c>
       <c r="F44" s="1"/>
     </row>
@@ -2947,12 +2944,12 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -2961,7 +2958,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -2980,13 +2977,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="B4" t="s">
-        <v>91</v>
-      </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -2994,13 +2991,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" t="s">
         <v>144</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>145</v>
-      </c>
-      <c r="C5" t="s">
-        <v>146</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -3011,10 +3008,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" t="s">
         <v>147</v>
-      </c>
-      <c r="C6" t="s">
-        <v>148</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -3022,13 +3019,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" t="s">
         <v>102</v>
       </c>
-      <c r="B7" t="s">
-        <v>103</v>
-      </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -3042,7 +3039,7 @@
         <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -3050,13 +3047,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" t="s">
         <v>106</v>
       </c>
-      <c r="B9" t="s">
-        <v>107</v>
-      </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -3070,7 +3067,7 @@
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -3078,13 +3075,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" t="s">
         <v>114</v>
       </c>
-      <c r="B11" t="s">
-        <v>115</v>
-      </c>
       <c r="C11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -3098,7 +3095,7 @@
         <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -3106,13 +3103,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" t="s">
         <v>121</v>
       </c>
-      <c r="B13" t="s">
-        <v>122</v>
-      </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -3126,7 +3123,7 @@
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
@@ -3140,7 +3137,7 @@
         <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -3154,7 +3151,7 @@
         <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
@@ -3162,13 +3159,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -3176,13 +3173,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" t="s">
         <v>133</v>
       </c>
-      <c r="B18" t="s">
-        <v>134</v>
-      </c>
       <c r="C18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -3190,13 +3187,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -3204,13 +3201,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" t="s">
         <v>136</v>
       </c>
-      <c r="B20" t="s">
-        <v>137</v>
-      </c>
       <c r="C20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -3218,13 +3215,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" t="s">
         <v>138</v>
       </c>
-      <c r="B21" t="s">
-        <v>139</v>
-      </c>
       <c r="C21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -3232,13 +3229,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s">
         <v>70</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>71</v>
-      </c>
-      <c r="C22" t="s">
-        <v>72</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
@@ -3246,13 +3243,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s">
         <v>73</v>
       </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
       <c r="C23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -3260,13 +3257,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
         <v>76</v>
       </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
       <c r="C24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -3274,13 +3271,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
         <v>82</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>84</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -3288,13 +3285,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>162</v>
+      </c>
+      <c r="B26" t="s">
         <v>163</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>164</v>
-      </c>
-      <c r="C26" t="s">
-        <v>165</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -3302,13 +3299,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" t="s">
         <v>85</v>
       </c>
-      <c r="B27" t="s">
-        <v>86</v>
-      </c>
       <c r="C27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -3339,16 +3336,16 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F1" t="s">
         <v>167</v>
       </c>
-      <c r="E1" t="s">
-        <v>341</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>168</v>
-      </c>
-      <c r="G1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -3362,16 +3359,16 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2" t="s">
         <v>351</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>170</v>
-      </c>
-      <c r="F2" t="s">
-        <v>352</v>
-      </c>
-      <c r="G2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -3382,7 +3379,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3393,13 +3390,13 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="B4" t="s">
-        <v>91</v>
-      </c>
       <c r="C4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -3407,13 +3404,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" t="s">
         <v>144</v>
       </c>
-      <c r="B5" t="s">
-        <v>145</v>
-      </c>
       <c r="C5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -3427,7 +3424,7 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -3447,7 +3444,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -3458,13 +3455,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" t="s">
         <v>98</v>
       </c>
-      <c r="B8" t="s">
-        <v>99</v>
-      </c>
       <c r="C8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -3472,13 +3469,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" t="s">
         <v>100</v>
       </c>
-      <c r="B9" t="s">
-        <v>101</v>
-      </c>
       <c r="C9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -3495,7 +3492,7 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -3509,7 +3506,7 @@
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -3529,7 +3526,7 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G12" t="s">
         <v>10</v>
@@ -3537,13 +3534,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" t="s">
         <v>104</v>
       </c>
-      <c r="B13" t="s">
-        <v>105</v>
-      </c>
       <c r="C13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F13" t="s">
         <v>10</v>
@@ -3551,13 +3548,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" t="s">
         <v>104</v>
       </c>
-      <c r="B14" t="s">
-        <v>105</v>
-      </c>
       <c r="C14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G14" t="s">
         <v>10</v>
@@ -3571,7 +3568,7 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G15" t="s">
         <v>10</v>
@@ -3579,13 +3576,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" t="s">
         <v>108</v>
       </c>
-      <c r="B16" t="s">
-        <v>109</v>
-      </c>
       <c r="C16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F16" t="s">
         <v>10</v>
@@ -3599,7 +3596,7 @@
         <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F17" t="s">
         <v>10</v>
@@ -3613,7 +3610,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -3630,7 +3627,7 @@
         <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F19" t="s">
         <v>10</v>
@@ -3644,7 +3641,7 @@
         <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G20" t="s">
         <v>10</v>
@@ -3658,7 +3655,7 @@
         <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -3678,7 +3675,7 @@
         <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G22" t="s">
         <v>10</v>
@@ -3686,13 +3683,13 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>353</v>
+      </c>
+      <c r="B23" t="s">
         <v>58</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>59</v>
-      </c>
-      <c r="C23" t="s">
-        <v>60</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -3709,13 +3706,13 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" t="s">
         <v>133</v>
       </c>
-      <c r="B24" t="s">
-        <v>134</v>
-      </c>
       <c r="C24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -3729,13 +3726,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -3743,13 +3740,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" t="s">
         <v>70</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>71</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -3763,13 +3760,13 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" t="s">
         <v>73</v>
       </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
       <c r="C27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>
@@ -3777,13 +3774,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" t="s">
         <v>73</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>74</v>
-      </c>
-      <c r="C28" t="s">
-        <v>75</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -3794,13 +3791,13 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" t="s">
         <v>76</v>
       </c>
-      <c r="B29" t="s">
-        <v>77</v>
-      </c>
       <c r="C29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -3808,13 +3805,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" t="s">
         <v>82</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>83</v>
-      </c>
-      <c r="C30" t="s">
-        <v>84</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -3831,13 +3828,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" t="s">
         <v>163</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>164</v>
-      </c>
-      <c r="C31" t="s">
-        <v>165</v>
       </c>
       <c r="F31" t="s">
         <v>10</v>
@@ -3845,13 +3842,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" t="s">
         <v>163</v>
       </c>
-      <c r="B32" t="s">
-        <v>164</v>
-      </c>
       <c r="C32" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G32" t="s">
         <v>10</v>
@@ -3859,13 +3856,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" t="s">
         <v>85</v>
       </c>
-      <c r="B33" t="s">
-        <v>86</v>
-      </c>
       <c r="C33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G33" t="s">
         <v>10</v>
@@ -3896,31 +3893,31 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E1" t="s">
         <v>198</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G1" t="s">
         <v>199</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I1" t="s">
         <v>338</v>
       </c>
-      <c r="G1" t="s">
-        <v>200</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>201</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
+        <v>202</v>
+      </c>
+      <c r="L1" t="s">
         <v>339</v>
-      </c>
-      <c r="J1" t="s">
-        <v>202</v>
-      </c>
-      <c r="K1" t="s">
-        <v>203</v>
-      </c>
-      <c r="L1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -3934,31 +3931,31 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" t="s">
         <v>204</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>205</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>206</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>207</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>208</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>209</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>210</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>211</v>
-      </c>
-      <c r="L2" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -4001,13 +3998,13 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="B4" t="s">
-        <v>91</v>
-      </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -4027,7 +4024,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4056,7 +4053,7 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -4102,13 +4099,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" t="s">
         <v>114</v>
       </c>
-      <c r="B8" t="s">
-        <v>115</v>
-      </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
@@ -4116,13 +4113,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" t="s">
         <v>114</v>
       </c>
-      <c r="B9" t="s">
-        <v>115</v>
-      </c>
       <c r="C9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4165,13 +4162,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" t="s">
         <v>96</v>
       </c>
-      <c r="B11" t="s">
-        <v>97</v>
-      </c>
       <c r="C11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L11" t="s">
         <v>10</v>
@@ -4179,13 +4176,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" t="s">
         <v>102</v>
       </c>
-      <c r="B12" t="s">
-        <v>103</v>
-      </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -4208,7 +4205,7 @@
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J13" t="s">
         <v>10</v>
@@ -4216,13 +4213,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" t="s">
         <v>104</v>
       </c>
-      <c r="B14" t="s">
-        <v>105</v>
-      </c>
       <c r="C14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
@@ -4253,13 +4250,13 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" t="s">
         <v>121</v>
       </c>
-      <c r="B16" t="s">
-        <v>122</v>
-      </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K16" t="s">
         <v>10</v>
@@ -4267,13 +4264,13 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" t="s">
         <v>123</v>
       </c>
-      <c r="B17" t="s">
-        <v>124</v>
-      </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -4284,13 +4281,13 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" t="s">
         <v>125</v>
       </c>
-      <c r="B18" t="s">
-        <v>126</v>
-      </c>
       <c r="C18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J18" t="s">
         <v>10</v>
@@ -4307,7 +4304,7 @@
         <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I19" t="s">
         <v>10</v>
@@ -4315,13 +4312,13 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" t="s">
         <v>127</v>
       </c>
-      <c r="B20" t="s">
-        <v>128</v>
-      </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J20" t="s">
         <v>10</v>
@@ -4375,13 +4372,13 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
         <v>59</v>
-      </c>
-      <c r="C23" t="s">
-        <v>60</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -4413,13 +4410,13 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" t="s">
         <v>133</v>
       </c>
-      <c r="B24" t="s">
-        <v>134</v>
-      </c>
       <c r="C24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -4451,13 +4448,13 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -4480,13 +4477,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" t="s">
         <v>138</v>
       </c>
-      <c r="B26" t="s">
-        <v>139</v>
-      </c>
       <c r="C26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
@@ -4497,13 +4494,13 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>223</v>
+      </c>
+      <c r="B27" t="s">
         <v>224</v>
       </c>
-      <c r="B27" t="s">
-        <v>225</v>
-      </c>
       <c r="C27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H27" t="s">
         <v>10</v>
@@ -4514,13 +4511,13 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
         <v>70</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>71</v>
-      </c>
-      <c r="C28" t="s">
-        <v>72</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -4552,13 +4549,13 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" t="s">
         <v>226</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>227</v>
-      </c>
-      <c r="C29" t="s">
-        <v>228</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -4569,13 +4566,13 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" t="s">
         <v>73</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>74</v>
-      </c>
-      <c r="C30" t="s">
-        <v>75</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -4586,13 +4583,13 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" t="s">
         <v>76</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>77</v>
-      </c>
-      <c r="C31" t="s">
-        <v>78</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -4624,13 +4621,13 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" t="s">
         <v>79</v>
       </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I32" t="s">
         <v>10</v>
@@ -4638,13 +4635,13 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" t="s">
         <v>82</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>83</v>
-      </c>
-      <c r="C33" t="s">
-        <v>84</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -4676,13 +4673,13 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" t="s">
         <v>85</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>86</v>
-      </c>
-      <c r="C34" t="s">
-        <v>87</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -4712,28 +4709,28 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" t="s">
         <v>229</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G1" t="s">
         <v>230</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>334</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
+        <v>335</v>
+      </c>
+      <c r="J1" t="s">
         <v>231</v>
       </c>
-      <c r="H1" t="s">
-        <v>335</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>336</v>
-      </c>
-      <c r="J1" t="s">
-        <v>232</v>
-      </c>
-      <c r="K1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -4747,28 +4744,28 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" t="s">
         <v>233</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>234</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>235</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>236</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>237</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>238</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>239</v>
-      </c>
-      <c r="K2" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -4808,13 +4805,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="B4" t="s">
-        <v>91</v>
-      </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -4849,7 +4846,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -4875,13 +4872,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" t="s">
         <v>242</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>243</v>
-      </c>
-      <c r="C6" t="s">
-        <v>244</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -4898,10 +4895,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4924,10 +4921,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" t="s">
         <v>246</v>
-      </c>
-      <c r="C8" t="s">
-        <v>247</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -4962,7 +4959,7 @@
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -4997,7 +4994,7 @@
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -5058,7 +5055,7 @@
         <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -5093,7 +5090,7 @@
         <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -5128,7 +5125,7 @@
         <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
@@ -5157,13 +5154,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" t="s">
         <v>133</v>
       </c>
-      <c r="B15" t="s">
-        <v>134</v>
-      </c>
       <c r="C15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -5192,13 +5189,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
@@ -5221,13 +5218,13 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
         <v>70</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>72</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -5256,13 +5253,13 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" t="s">
         <v>76</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>78</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -5291,13 +5288,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" t="s">
         <v>79</v>
       </c>
-      <c r="B19" t="s">
-        <v>80</v>
-      </c>
       <c r="C19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -5314,13 +5311,13 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>353</v>
+      </c>
+      <c r="B20" t="s">
         <v>58</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -5349,13 +5346,13 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
         <v>82</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -5384,13 +5381,13 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" t="s">
         <v>163</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>164</v>
-      </c>
-      <c r="C22" t="s">
-        <v>165</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
@@ -5419,13 +5416,13 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" t="s">
         <v>85</v>
       </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
       <c r="C23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -5473,25 +5470,25 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E1" t="s">
         <v>251</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G1" t="s">
         <v>252</v>
       </c>
-      <c r="F1" t="s">
-        <v>342</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>253</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>254</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>255</v>
-      </c>
-      <c r="J1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -5505,25 +5502,25 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E2" t="s">
         <v>257</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>258</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>259</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>260</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>261</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>262</v>
-      </c>
-      <c r="J2" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -5545,13 +5542,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="B4" t="s">
-        <v>91</v>
-      </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J4" t="s">
         <v>10</v>
@@ -5559,13 +5556,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" t="s">
         <v>144</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>145</v>
-      </c>
-      <c r="C5" t="s">
-        <v>146</v>
       </c>
       <c r="H5" t="s">
         <v>10</v>
@@ -5582,10 +5579,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -5599,10 +5596,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" t="s">
         <v>147</v>
-      </c>
-      <c r="C7" t="s">
-        <v>148</v>
       </c>
       <c r="F7" t="s">
         <v>10</v>
@@ -5622,7 +5619,7 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -5653,13 +5650,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -5685,7 +5682,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H11" t="s">
         <v>10</v>
@@ -5702,7 +5699,7 @@
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J12" t="s">
         <v>10</v>
@@ -5716,7 +5713,7 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -5759,7 +5756,7 @@
         <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H15" t="s">
         <v>10</v>
@@ -5767,13 +5764,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" t="s">
         <v>123</v>
       </c>
-      <c r="B16" t="s">
-        <v>124</v>
-      </c>
       <c r="C16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J16" t="s">
         <v>10</v>
@@ -5787,7 +5784,7 @@
         <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -5816,7 +5813,7 @@
         <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H18" t="s">
         <v>10</v>
@@ -5827,13 +5824,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" t="s">
         <v>129</v>
       </c>
-      <c r="B19" t="s">
-        <v>130</v>
-      </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -5853,7 +5850,7 @@
         <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J20" t="s">
         <v>10</v>
@@ -5861,13 +5858,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
         <v>59</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -5890,13 +5887,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H22" t="s">
         <v>10</v>
@@ -5907,13 +5904,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" t="s">
         <v>136</v>
       </c>
-      <c r="B23" t="s">
-        <v>137</v>
-      </c>
       <c r="C23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J23" t="s">
         <v>10</v>
@@ -5921,13 +5918,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
         <v>138</v>
       </c>
-      <c r="B24" t="s">
-        <v>139</v>
-      </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J24" t="s">
         <v>10</v>
@@ -5935,13 +5932,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" t="s">
         <v>70</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>71</v>
-      </c>
-      <c r="C25" t="s">
-        <v>72</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -5964,13 +5961,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>269</v>
+      </c>
+      <c r="B26" t="s">
         <v>270</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>271</v>
-      </c>
-      <c r="C26" t="s">
-        <v>272</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -5981,13 +5978,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>272</v>
+      </c>
+      <c r="B27" t="s">
         <v>273</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>274</v>
-      </c>
-      <c r="C27" t="s">
-        <v>275</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -5998,13 +5995,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>225</v>
+      </c>
+      <c r="B28" t="s">
         <v>226</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>227</v>
-      </c>
-      <c r="C28" t="s">
-        <v>228</v>
       </c>
       <c r="J28" t="s">
         <v>10</v>
@@ -6012,13 +6009,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" t="s">
         <v>73</v>
       </c>
-      <c r="B29" t="s">
-        <v>74</v>
-      </c>
       <c r="C29" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -6035,13 +6032,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" t="s">
         <v>73</v>
       </c>
-      <c r="B30" t="s">
-        <v>74</v>
-      </c>
       <c r="C30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I30" t="s">
         <v>10</v>
@@ -6049,13 +6046,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" t="s">
         <v>73</v>
       </c>
-      <c r="B31" t="s">
-        <v>74</v>
-      </c>
       <c r="C31" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H31" t="s">
         <v>10</v>
@@ -6066,13 +6063,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" t="s">
         <v>76</v>
       </c>
-      <c r="B32" t="s">
-        <v>77</v>
-      </c>
       <c r="C32" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H32" t="s">
         <v>10</v>
@@ -6086,13 +6083,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" t="s">
         <v>79</v>
       </c>
-      <c r="B33" t="s">
-        <v>80</v>
-      </c>
       <c r="C33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J33" t="s">
         <v>10</v>
@@ -6100,13 +6097,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" t="s">
         <v>82</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>83</v>
-      </c>
-      <c r="C34" t="s">
-        <v>84</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -6129,13 +6126,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" t="s">
         <v>163</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>164</v>
-      </c>
-      <c r="C35" t="s">
-        <v>165</v>
       </c>
       <c r="J35" t="s">
         <v>10</v>
@@ -6143,13 +6140,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" t="s">
         <v>85</v>
       </c>
-      <c r="B36" t="s">
-        <v>86</v>
-      </c>
       <c r="C36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H36" t="s">
         <v>10</v>
@@ -6160,13 +6157,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>279</v>
+      </c>
+      <c r="B37" t="s">
         <v>280</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>281</v>
-      </c>
-      <c r="C37" t="s">
-        <v>282</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -6187,25 +6184,25 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F1" t="s">
         <v>283</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>284</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>285</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>343</v>
+      </c>
+      <c r="J1" t="s">
         <v>286</v>
-      </c>
-      <c r="I1" t="s">
-        <v>344</v>
-      </c>
-      <c r="J1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -6219,25 +6216,25 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E2" t="s">
         <v>288</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>289</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>290</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>291</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>342</v>
+      </c>
+      <c r="J2" t="s">
         <v>292</v>
-      </c>
-      <c r="I2" t="s">
-        <v>343</v>
-      </c>
-      <c r="J2" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -6268,13 +6265,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="B4" t="s">
-        <v>91</v>
-      </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
@@ -6282,13 +6279,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5" t="s">
         <v>294</v>
-      </c>
-      <c r="C5" t="s">
-        <v>295</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -6299,13 +6296,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" t="s">
         <v>144</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>145</v>
-      </c>
-      <c r="C6" t="s">
-        <v>146</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -6322,10 +6319,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -6354,7 +6351,7 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -6449,7 +6446,7 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -6463,13 +6460,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" t="s">
         <v>106</v>
       </c>
-      <c r="B13" t="s">
-        <v>107</v>
-      </c>
       <c r="C13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -6506,7 +6503,7 @@
         <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F15" t="s">
         <v>10</v>
@@ -6514,13 +6511,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" t="s">
         <v>112</v>
       </c>
-      <c r="B16" t="s">
-        <v>113</v>
-      </c>
       <c r="C16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J16" t="s">
         <v>10</v>
@@ -6528,13 +6525,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" t="s">
         <v>114</v>
       </c>
-      <c r="B17" t="s">
-        <v>115</v>
-      </c>
       <c r="C17" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H17" t="s">
         <v>10</v>
@@ -6545,13 +6542,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B18" t="s">
+        <v>299</v>
+      </c>
+      <c r="C18" t="s">
         <v>300</v>
-      </c>
-      <c r="C18" t="s">
-        <v>301</v>
       </c>
       <c r="I18" t="s">
         <v>10</v>
@@ -6559,13 +6556,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s">
+        <v>301</v>
+      </c>
+      <c r="C19" t="s">
         <v>302</v>
-      </c>
-      <c r="C19" t="s">
-        <v>303</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -6597,7 +6594,7 @@
         <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -6617,7 +6614,7 @@
         <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -6637,18 +6634,18 @@
         <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
         <v>59</v>
-      </c>
-      <c r="C23" t="s">
-        <v>60</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -6674,13 +6671,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" t="s">
         <v>133</v>
       </c>
-      <c r="B24" t="s">
-        <v>134</v>
-      </c>
       <c r="C24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I24" t="s">
         <v>10</v>
@@ -6688,13 +6685,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -6711,13 +6708,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" t="s">
         <v>136</v>
       </c>
-      <c r="B26" t="s">
-        <v>137</v>
-      </c>
       <c r="C26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -6734,13 +6731,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" t="s">
         <v>70</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>71</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
       </c>
       <c r="I27" t="s">
         <v>10</v>
@@ -6748,13 +6745,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" t="s">
         <v>67</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>68</v>
-      </c>
-      <c r="C28" t="s">
-        <v>69</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -6777,13 +6774,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" t="s">
         <v>73</v>
       </c>
-      <c r="B29" t="s">
-        <v>74</v>
-      </c>
       <c r="C29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -6803,13 +6800,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" t="s">
         <v>76</v>
       </c>
-      <c r="B30" t="s">
-        <v>77</v>
-      </c>
       <c r="C30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -6829,13 +6826,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>304</v>
+      </c>
+      <c r="B31" t="s">
         <v>305</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>306</v>
-      </c>
-      <c r="C31" t="s">
-        <v>307</v>
       </c>
       <c r="J31" t="s">
         <v>10</v>
@@ -6843,13 +6840,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" t="s">
         <v>82</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>83</v>
-      </c>
-      <c r="C32" t="s">
-        <v>84</v>
       </c>
       <c r="H32" t="s">
         <v>10</v>
@@ -6883,13 +6880,13 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" t="s">
         <v>308</v>
-      </c>
-      <c r="E1" t="s">
-        <v>345</v>
-      </c>
-      <c r="F1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -6903,13 +6900,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E2" t="s">
         <v>310</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>311</v>
-      </c>
-      <c r="F2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -6928,13 +6925,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="B4" t="s">
-        <v>91</v>
-      </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -6942,13 +6939,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" t="s">
         <v>92</v>
       </c>
-      <c r="B5" t="s">
-        <v>93</v>
-      </c>
       <c r="C5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6962,7 +6959,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -6979,7 +6976,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -6996,7 +6993,7 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -7010,7 +7007,7 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -7027,7 +7024,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -7041,7 +7038,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -7058,7 +7055,7 @@
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -7072,7 +7069,7 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -7080,13 +7077,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" t="s">
         <v>116</v>
       </c>
-      <c r="B14" t="s">
-        <v>117</v>
-      </c>
       <c r="C14" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F14" t="s">
         <v>10</v>
@@ -7094,13 +7091,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" t="s">
         <v>118</v>
       </c>
-      <c r="B15" t="s">
-        <v>119</v>
-      </c>
       <c r="C15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -7131,7 +7128,7 @@
         <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -7145,7 +7142,7 @@
         <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -7159,7 +7156,7 @@
         <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -7167,13 +7164,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -7187,13 +7184,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" t="s">
         <v>131</v>
       </c>
-      <c r="B21" t="s">
-        <v>132</v>
-      </c>
       <c r="C21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -7201,13 +7198,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" t="s">
         <v>133</v>
       </c>
-      <c r="B22" t="s">
-        <v>134</v>
-      </c>
       <c r="C22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
@@ -7215,13 +7212,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C23" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -7232,13 +7229,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s">
         <v>73</v>
       </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
       <c r="C24" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -7249,13 +7246,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" t="s">
         <v>76</v>
       </c>
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
       <c r="C25" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -7266,13 +7263,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" t="s">
         <v>82</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>84</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -7286,13 +7283,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>162</v>
+      </c>
+      <c r="B27" t="s">
         <v>163</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>164</v>
-      </c>
-      <c r="C27" t="s">
-        <v>165</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -7300,13 +7297,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" t="s">
         <v>85</v>
       </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
       <c r="C28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -7314,13 +7311,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>318</v>
+      </c>
+      <c r="B29" t="s">
         <v>319</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>320</v>
-      </c>
-      <c r="C29" t="s">
-        <v>321</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
